--- a/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/JLCPCB-BOM-Termination-Board-V1.0.1.xlsx
+++ b/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/JLCPCB-BOM-Termination-Board-V1.0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.0\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,19 +33,19 @@
     <t>1uF</t>
   </si>
   <si>
-    <t>B260A-13-F</t>
+    <t>SS510B</t>
   </si>
   <si>
     <t>SMBJ26CA</t>
   </si>
   <si>
-    <t>BSMD1812-110-33V</t>
-  </si>
-  <si>
-    <t>S5B-PH-SM4-TB(LF)(SN)</t>
-  </si>
-  <si>
-    <t>PJ-051AH</t>
+    <t>BSMD2920-330-30V</t>
+  </si>
+  <si>
+    <t>S5B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>DC-003A-3.5A-1.3</t>
   </si>
   <si>
     <t>Designator</t>
@@ -87,13 +87,10 @@
     <t>Cap-0805</t>
   </si>
   <si>
-    <t>SMA</t>
-  </si>
-  <si>
     <t>SMB Bi Directional</t>
   </si>
   <si>
-    <t>Fuse-1812_</t>
+    <t>Fuse-2920</t>
   </si>
   <si>
     <t>LCSC Part Number</t>
@@ -108,19 +105,22 @@
     <t>C2842838</t>
   </si>
   <si>
-    <t>C109094</t>
+    <t>C3011128</t>
   </si>
   <si>
     <t>C5331111</t>
   </si>
   <si>
-    <t>C883154</t>
-  </si>
-  <si>
-    <t>C22359773</t>
-  </si>
-  <si>
-    <t>C265104</t>
+    <t>C22368176</t>
+  </si>
+  <si>
+    <t>C263757</t>
+  </si>
+  <si>
+    <t>C779945</t>
+  </si>
+  <si>
+    <t>SMB</t>
   </si>
 </sst>
 </file>
@@ -586,7 +586,7 @@
         <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -600,7 +600,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -614,7 +614,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -628,7 +628,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -639,10 +639,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -653,10 +653,10 @@
         <v>14</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -667,10 +667,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">

--- a/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/JLCPCB-BOM-Termination-Board-V1.0.1.xlsx
+++ b/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/JLCPCB-BOM-Termination-Board-V1.0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -99,9 +99,6 @@
     <t>C72523</t>
   </si>
   <si>
-    <t>C327087</t>
-  </si>
-  <si>
     <t>C2842838</t>
   </si>
   <si>
@@ -121,6 +118,9 @@
   </si>
   <si>
     <t>SMB</t>
+  </si>
+  <si>
+    <t>C91183</t>
   </si>
 </sst>
 </file>
@@ -567,15 +567,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -603,7 +603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -614,10 +614,10 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -628,10 +628,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -639,13 +639,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -656,10 +656,10 @@
         <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -670,10 +670,10 @@
         <v>23</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -684,10 +684,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/JLCPCB-BOM-Termination-Board-V1.0.1.xlsx
+++ b/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/JLCPCB-BOM-Termination-Board-V1.0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -45,7 +45,7 @@
     <t>S5B-XH-A(LF)(SN)</t>
   </si>
   <si>
-    <t>DC-003A-3.5A-1.3</t>
+    <t>DC-044K-D025</t>
   </si>
   <si>
     <t>Designator</t>
@@ -99,6 +99,9 @@
     <t>C72523</t>
   </si>
   <si>
+    <t>C91183</t>
+  </si>
+  <si>
     <t>C2842838</t>
   </si>
   <si>
@@ -114,13 +117,10 @@
     <t>C263757</t>
   </si>
   <si>
-    <t>C779945</t>
+    <t>C963204</t>
   </si>
   <si>
     <t>SMB</t>
-  </si>
-  <si>
-    <t>C91183</t>
   </si>
 </sst>
 </file>
@@ -567,15 +567,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -603,7 +603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -614,10 +614,10 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -628,10 +628,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -639,13 +639,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -656,10 +656,10 @@
         <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -670,10 +670,10 @@
         <v>23</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -684,10 +684,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
